--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_19_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_19_5.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_24</t>
+          <t>model_19_5_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9908501787241604</v>
+        <v>0.9998544300569741</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8113604644612539</v>
+        <v>0.6389774991397066</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7395541545611217</v>
+        <v>0.9999903710428117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9918274386570766</v>
+        <v>0.9999999999789906</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9756845896135712</v>
+        <v>0.9999932163819603</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06118489700259246</v>
+        <v>8.641660647434658e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.261433442752788</v>
+        <v>0.2143185518706699</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2944608691674422</v>
+        <v>9.476429227560987e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07256474791583944</v>
+        <v>8.35177135385366e-12</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1835127385822111</v>
+        <v>4.73821878966617e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5116686842603354</v>
+        <v>0.001577299796810224</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2473558105292707</v>
+        <v>0.009296053274069948</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002413139677145</v>
+        <v>1.000065918464766</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2578862594806184</v>
+        <v>0.009691805507430233</v>
       </c>
       <c r="P2" t="n">
-        <v>235.5877098018454</v>
+        <v>172.712661392118</v>
       </c>
       <c r="Q2" t="n">
-        <v>375.7584296616885</v>
+        <v>266.5660999069694</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_23</t>
+          <t>model_19_5_0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9909268530668358</v>
+        <v>0.999854370104604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8109360381370617</v>
+        <v>0.6389774898115766</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7446423827332587</v>
+        <v>0.9999903696646975</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9919457218181869</v>
+        <v>0.9999999999986207</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9761352660330029</v>
+        <v>0.999993215416663</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0606721753200688</v>
+        <v>8.645219679096467e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.264271583536965</v>
+        <v>0.2143185574082507</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2887081028387454</v>
+        <v>9.477785511801584e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07151450339536396</v>
+        <v>5.483276709987273e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1801114032713954</v>
+        <v>4.738893030064629e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5100271959898501</v>
+        <v>0.001575837935165267</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2463172249763885</v>
+        <v>0.009297967347273525</v>
       </c>
       <c r="N3" t="n">
-        <v>1.002392917872483</v>
+        <v>1.000065945613009</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2568034591905816</v>
+        <v>0.009693801066692764</v>
       </c>
       <c r="P3" t="n">
-        <v>235.6045401654331</v>
+        <v>172.711837870084</v>
       </c>
       <c r="Q3" t="n">
-        <v>375.7752600252762</v>
+        <v>266.5652763849354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_22</t>
+          <t>model_19_5_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9909990340021874</v>
+        <v>0.9995192444213244</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8104595043838441</v>
+        <v>0.6386147529800065</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7502168918360064</v>
+        <v>0.9999621756311624</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9920756546510516</v>
+        <v>0.9956065396434747</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9766292698070549</v>
+        <v>0.9987231316795755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06018950107301046</v>
+        <v>0.0002853972790614479</v>
       </c>
       <c r="H4" t="n">
-        <v>1.267458166938968</v>
+        <v>0.214533893660886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2824055458030943</v>
+        <v>3.722521009910802e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07036082061866762</v>
+        <v>0.001746507727775028</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1763830686882861</v>
+        <v>0.0008918664689370681</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5082072597609424</v>
+        <v>0.003937512207988295</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2453354867788402</v>
+        <v>0.01689370530882577</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00237388114228</v>
+        <v>1.0002177006394</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2557799263654854</v>
+        <v>0.01761290531861349</v>
       </c>
       <c r="P4" t="n">
-        <v>235.620514685315</v>
+        <v>170.3232567734781</v>
       </c>
       <c r="Q4" t="n">
-        <v>375.7912345451581</v>
+        <v>264.1766952883295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_21</t>
+          <t>model_19_5_4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9910633040342608</v>
+        <v>0.9995192789229408</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8099240483171237</v>
+        <v>0.6386147452674361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7563177531478951</v>
+        <v>0.9999621806209957</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9922181119985815</v>
+        <v>0.995606849331084</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9771700237886166</v>
+        <v>0.998723223320889</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05975972707259933</v>
+        <v>0.0002853767974116014</v>
       </c>
       <c r="H5" t="n">
-        <v>1.271038764122674</v>
+        <v>0.2145338982394009</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2755078933504643</v>
+        <v>3.722029930739233e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06909593179391615</v>
+        <v>0.001746384619391403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1723019019516955</v>
+        <v>0.0008918024593493978</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5061817270943482</v>
+        <v>0.003937380709612915</v>
       </c>
       <c r="M5" t="n">
-        <v>0.244458027220624</v>
+        <v>0.0168930991061913</v>
       </c>
       <c r="N5" t="n">
-        <v>1.002356930804151</v>
+        <v>1.000217685016027</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2548651115372842</v>
+        <v>0.01761227330867787</v>
       </c>
       <c r="P5" t="n">
-        <v>235.6348466104525</v>
+        <v>170.3234003094283</v>
       </c>
       <c r="Q5" t="n">
-        <v>375.8055664702956</v>
+        <v>264.1768388242798</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_20</t>
+          <t>model_19_5_2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.991115028886696</v>
+        <v>0.9995193571327354</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8093216877226368</v>
+        <v>0.6386147402643354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7629804460459915</v>
+        <v>0.9999621905241322</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9923739917457934</v>
+        <v>0.995607554857782</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9777607520436077</v>
+        <v>0.9987234310652168</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05941384274619432</v>
+        <v>0.0002853303686989863</v>
       </c>
       <c r="H6" t="n">
-        <v>1.275066752191624</v>
+        <v>0.2145339012094577</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2679750323886656</v>
+        <v>3.721055304209234e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06771186453678613</v>
+        <v>0.001746104155308409</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1678435704611523</v>
+        <v>0.0008916573541752505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5039368013034954</v>
+        <v>0.003937083294064236</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2437495492225459</v>
+        <v>0.0168917248586101</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002343289084827</v>
+        <v>1.000217649600271</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2541264721640763</v>
+        <v>0.01761084055653204</v>
       </c>
       <c r="P6" t="n">
-        <v>235.6464560737972</v>
+        <v>170.3237257212365</v>
       </c>
       <c r="Q6" t="n">
-        <v>375.8171759336402</v>
+        <v>264.1771642360879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_19</t>
+          <t>model_19_5_3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9911483097214844</v>
+        <v>0.9995193221089247</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8086434168313307</v>
+        <v>0.6386147188308828</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7702425845380949</v>
+        <v>0.9999621849026885</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9925443580864638</v>
+        <v>0.9956072418304212</v>
       </c>
       <c r="F7" t="n">
-        <v>0.978404955419422</v>
+        <v>0.9987233424250086</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05919129365072034</v>
+        <v>0.0002853511603460142</v>
       </c>
       <c r="H7" t="n">
-        <v>1.279602352764939</v>
+        <v>0.2145339139332809</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2597644364054751</v>
+        <v>3.721608543898014e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06619916979576872</v>
+        <v>0.001746228591324746</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1629816526970349</v>
+        <v>0.000891719267552048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5014433216523678</v>
+        <v>0.003937225115087353</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2432926091165129</v>
+        <v>0.01689234028623667</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002334511721806</v>
+        <v>1.00021766546011</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2536500791717331</v>
+        <v>0.01761148218418679</v>
       </c>
       <c r="P7" t="n">
-        <v>235.6539616292367</v>
+        <v>170.3235799891882</v>
       </c>
       <c r="Q7" t="n">
-        <v>375.8246814890798</v>
+        <v>264.1770185040397</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_18</t>
+          <t>model_19_5_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9911555356284056</v>
+        <v>0.9995190692540751</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8078786600179564</v>
+        <v>0.6386146754152606</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7781413842267851</v>
+        <v>0.9999621543379517</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9927300577309303</v>
+        <v>0.9956049573285588</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9791058098329107</v>
+        <v>0.9987226708061224</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05914297397786549</v>
+        <v>0.0002855012659074833</v>
       </c>
       <c r="H8" t="n">
-        <v>1.284716285097353</v>
+        <v>0.2145339397066698</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2508340293268292</v>
+        <v>3.724616601372141e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06455032957012267</v>
+        <v>0.001747136736575373</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1576921794484759</v>
+        <v>0.0008921883796405026</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4986766263498137</v>
+        <v>0.003937910874084586</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2431932852236375</v>
+        <v>0.0168967827087728</v>
       </c>
       <c r="N8" t="n">
-        <v>1.002332605988113</v>
+        <v>1.000217779960419</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2535465268551091</v>
+        <v>0.01761611372984736</v>
       </c>
       <c r="P8" t="n">
-        <v>235.6555949574859</v>
+        <v>170.3225281897527</v>
       </c>
       <c r="Q8" t="n">
-        <v>375.8263148173289</v>
+        <v>264.1759667046041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_17</t>
+          <t>model_19_5_22</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9911269192526884</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8070153556035836</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7867077478741382</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9929319856468988</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9798662120768686</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05933433181405315</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H9" t="n">
-        <v>1.290489205691416</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2411488723954397</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0627573973785383</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1519532881036414</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4956086612882029</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2435863949691221</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N9" t="n">
-        <v>1.002340153164126</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2539563720963084</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P9" t="n">
-        <v>235.649134378346</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q9" t="n">
-        <v>375.8198542381891</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_16</t>
+          <t>model_19_5_21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9910501045619675</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8060395036152807</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7959731943433761</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9931508868378163</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F10" t="n">
-        <v>0.980689035888237</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05984799200460255</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H10" t="n">
-        <v>1.297014732430583</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2306733302881786</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06081375828292459</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1457432900573348</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4922047533663804</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2446384924835063</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N10" t="n">
-        <v>1.002360411983657</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O10" t="n">
-        <v>0.255053259580022</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P10" t="n">
-        <v>235.6318947960142</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q10" t="n">
-        <v>375.8026146558573</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_15</t>
+          <t>model_19_5_20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9909093898859376</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8049348876560926</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8059606462653411</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9933874329264647</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9815762265320356</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06078895169114607</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H11" t="n">
-        <v>1.304401304435963</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2193814866085294</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05871344889728537</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1390475040475348</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4885229527230356</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2465541556963623</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N11" t="n">
-        <v>1.002397523546566</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2570504765418188</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P11" t="n">
-        <v>235.6006944442569</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q11" t="n">
-        <v>375.7714143040999</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_14</t>
+          <t>model_19_5_19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9906849634524831</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8036826100880246</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8166842268980093</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9936420217765068</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9825292163513365</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06228969228504459</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H12" t="n">
-        <v>1.312775290299841</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2072573735578427</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05645293656213071</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1318551199256329</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L12" t="n">
-        <v>0.484445665711501</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2495790301388412</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N12" t="n">
-        <v>1.002456712935609</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2602041261516673</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P12" t="n">
-        <v>235.5519186395322</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q12" t="n">
-        <v>375.7226384993753</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_13</t>
+          <t>model_19_5_18</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9903519486370086</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8022605760848359</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8281495446772963</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9939146952573369</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9835483565791201</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06451656388951502</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H13" t="n">
-        <v>1.322284438227028</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1942946502213245</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05403184951615793</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1241634868736881</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4799754920415388</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2540011100163049</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N13" t="n">
-        <v>1.002544541018811</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O13" t="n">
-        <v>0.264814463124482</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P13" t="n">
-        <v>235.4816665673209</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q13" t="n">
-        <v>375.6523864271639</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_12</t>
+          <t>model_19_5_17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9898790936634436</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8006431464628303</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8403440009798484</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9942051374833873</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9846326431607162</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06767854727504112</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H14" t="n">
-        <v>1.333100197556958</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1805075606410587</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05145299252957664</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1159801826713576</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4789746244881753</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2601510085989311</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N14" t="n">
-        <v>1.002669250022828</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2712261756218157</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P14" t="n">
-        <v>235.3859720570536</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q14" t="n">
-        <v>375.5566919168967</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_11</t>
+          <t>model_19_5_16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9892273725006505</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7988000779644414</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8532394966386546</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9945123894187481</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9857792710654374</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07203660969153841</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H15" t="n">
-        <v>1.345424805092235</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1659278738211813</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04872488094979431</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1073263773854878</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4776546746815186</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2683963667629247</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N15" t="n">
-        <v>1.002841132527301</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2798225557530949</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P15" t="n">
-        <v>235.2611616425081</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q15" t="n">
-        <v>375.4318815023512</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_10</t>
+          <t>model_19_5_15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9883480039306836</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7966959887730556</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8667808828289343</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9948347940883721</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9869831806517172</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07791695136802773</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H16" t="n">
-        <v>1.359494859203472</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1506179411916069</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.04586222717498848</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09824025703331454</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4759247710655103</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2791360803766287</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N16" t="n">
-        <v>1.003073053908391</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2910194812096063</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P16" t="n">
-        <v>235.1042234911338</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q16" t="n">
-        <v>375.2749433509769</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_9</t>
+          <t>model_19_5_12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.98718007885918</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7942888562710066</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D17" t="n">
-        <v>0.880883918090144</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9951695612621271</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9882364769801999</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08572687169897242</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H17" t="n">
-        <v>1.375591365328499</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1346730064051948</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.04288980585507203</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08878140613013343</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4736863584228853</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2927915157564721</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N17" t="n">
-        <v>1.003381078103073</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3052562567442177</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P17" t="n">
-        <v>234.9131778942254</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q17" t="n">
-        <v>375.0838977540685</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_8</t>
+          <t>model_19_5_13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9856478194400967</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7915289764054325</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8954281221827816</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9955127311254443</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9895277479971463</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09597309748978841</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H18" t="n">
-        <v>1.394046694697671</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1182292847890947</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03984277646256868</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07903595348073347</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4707956070008305</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3097952509154852</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003785190477337</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3229838761115342</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P18" t="n">
-        <v>234.6873747225374</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q18" t="n">
-        <v>374.8580945823804</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_7</t>
+          <t>model_19_5_23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9836566978606929</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7883570719001192</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9102461400926208</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9958586253624832</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9908411104534182</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1092877366595336</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H19" t="n">
-        <v>1.415257234729979</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1014759884340796</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03677155716386019</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0691237727989699</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4670782835212527</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3305869577880131</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N19" t="n">
-        <v>1.004310321443334</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3446607289903923</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P19" t="n">
-        <v>234.4275421780016</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q19" t="n">
-        <v>374.5982620378446</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_6</t>
+          <t>model_19_5_11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9810890600139522</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7847017731940853</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9251182036524912</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9961994560226037</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9921555673322481</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1264575427635729</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H20" t="n">
-        <v>1.439700234008331</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08466158790189454</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03374529772133442</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05920333231498202</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4622984662912248</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M20" t="n">
-        <v>0.355608693318334</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N20" t="n">
-        <v>1.004987500655661</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3707476916043721</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P20" t="n">
-        <v>234.135697314957</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q20" t="n">
-        <v>374.3064171748001</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_5</t>
+          <t>model_19_5_10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9777981146168141</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C21" t="n">
-        <v>0.78047648090744</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9397581905045418</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9965246184884199</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9934433952111436</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1484641097876466</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H21" t="n">
-        <v>1.46795478298481</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06810957400514604</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03085815727985283</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K21" t="n">
-        <v>0.04948386564249943</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4561634545859598</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3853104070585773</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N21" t="n">
-        <v>1.005855442298862</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4017138687895611</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P21" t="n">
-        <v>233.8148240697631</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q21" t="n">
-        <v>373.9855439296062</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_4</t>
+          <t>model_19_5_14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.973600650854566</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7755746144631855</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9538061541072042</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9968201930799491</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9946694958978256</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1765325692933425</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H22" t="n">
-        <v>1.500733586468559</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I22" t="n">
-        <v>0.05222690340426922</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02823372965861395</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K22" t="n">
-        <v>0.04023026509804278</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4482684042785583</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4201577909468566</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N22" t="n">
-        <v>1.006962465708686</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4380447779539936</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P22" t="n">
-        <v>233.4684997821158</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q22" t="n">
-        <v>373.6392196419589</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_3</t>
+          <t>model_19_5_24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9682669838421412</v>
+        <v>0.9995190265115553</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7698622815104246</v>
+        <v>0.6386145456374794</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9668131457848943</v>
+        <v>0.999962157273998</v>
       </c>
       <c r="E23" t="n">
-        <v>0.997067331768099</v>
+        <v>0.9956045511095843</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9957891329553291</v>
+        <v>0.9987225528816128</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2121988251647064</v>
+        <v>0.0002855266397135925</v>
       </c>
       <c r="H23" t="n">
-        <v>1.538931983226546</v>
+        <v>0.2145340167483668</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03752115884454206</v>
+        <v>3.724327647592987e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.02603936783575812</v>
+        <v>0.001747298218532786</v>
       </c>
       <c r="K23" t="n">
-        <v>0.03178016454965651</v>
+        <v>0.0008922707475043578</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4381033009166951</v>
+        <v>0.003938001823746562</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4606504370612345</v>
+        <v>0.01689753353935398</v>
       </c>
       <c r="N23" t="n">
-        <v>1.008369147118556</v>
+        <v>1.000217799315522</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4802612798447936</v>
+        <v>0.01761689652484081</v>
       </c>
       <c r="P23" t="n">
-        <v>233.1004631785408</v>
+        <v>170.3223504484838</v>
       </c>
       <c r="Q23" t="n">
-        <v>373.2711830383839</v>
+        <v>264.1757889633353</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_2</t>
+          <t>model_19_5_9</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9615084526274952</v>
+        <v>0.9995190276981889</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7631667439259564</v>
+        <v>0.6386145420339425</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9782313230551705</v>
+        <v>0.9999621577744044</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9972405672655595</v>
+        <v>0.9956045609469597</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9967462732942031</v>
+        <v>0.9987225604313255</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2573931545172184</v>
+        <v>0.0002855259352766991</v>
       </c>
       <c r="H24" t="n">
-        <v>1.583705073884001</v>
+        <v>0.2145340188875819</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02461173271164377</v>
+        <v>3.724278399615195e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02450119764946986</v>
+        <v>0.001747294307935957</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02455645571633571</v>
+        <v>0.0008922654741841122</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4250225051989417</v>
+        <v>0.003937919286318398</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5073392893490691</v>
+        <v>0.01689751269497079</v>
       </c>
       <c r="N24" t="n">
-        <v>1.010151616889452</v>
+        <v>1.000217798778179</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5289377732337692</v>
+        <v>0.01761687479306909</v>
       </c>
       <c r="P24" t="n">
-        <v>232.7143011578019</v>
+        <v>170.3223553827888</v>
       </c>
       <c r="Q24" t="n">
-        <v>372.885021017645</v>
+        <v>264.1757938976402</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_1</t>
+          <t>model_19_5_8</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9529600747498876</v>
+        <v>0.9995190276981889</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7552565488132579</v>
+        <v>0.6386145420339425</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9874027196910797</v>
+        <v>0.9999621577744044</v>
       </c>
       <c r="E25" t="n">
-        <v>0.997303775689912</v>
+        <v>0.9956045609469597</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9974704129468631</v>
+        <v>0.9987225604313255</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3145561967464408</v>
+        <v>0.0002855259352766991</v>
       </c>
       <c r="H25" t="n">
-        <v>1.636600585025715</v>
+        <v>0.2145340188875819</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01424252363350174</v>
+        <v>3.724278399615195e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.02393996559664872</v>
+        <v>0.001747294307935957</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01909124461507523</v>
+        <v>0.0008922654741841122</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4082107554165714</v>
+        <v>0.003937919286318398</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5608530972959326</v>
+        <v>0.01689751269497079</v>
       </c>
       <c r="N25" t="n">
-        <v>1.012406134131898</v>
+        <v>1.000217798778179</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5847297747737846</v>
+        <v>0.01761687479306909</v>
       </c>
       <c r="P25" t="n">
-        <v>232.3131850656117</v>
+        <v>170.3223553827888</v>
       </c>
       <c r="Q25" t="n">
-        <v>372.4839049254548</v>
+        <v>264.1757938976402</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_19_5_0</t>
+          <t>model_19_5_7</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9421569007296876</v>
+        <v>0.9995190343218727</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7458057902431428</v>
+        <v>0.6386145415434541</v>
       </c>
       <c r="D26" t="n">
-        <v>0.993547820734299</v>
+        <v>0.9999621559417509</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9972020319510859</v>
+        <v>0.9956046273080442</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9978708454735254</v>
+        <v>0.9987225736263877</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3867970711635605</v>
+        <v>0.0002855220031717958</v>
       </c>
       <c r="H26" t="n">
-        <v>1.699797851100816</v>
+        <v>0.2145340191787571</v>
       </c>
       <c r="I26" t="n">
-        <v>0.007294853605366265</v>
+        <v>3.724458761957047e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02484335542147116</v>
+        <v>0.001747267927785112</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0160691089234558</v>
+        <v>0.0008922562577023416</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3867210230063206</v>
+        <v>0.003937934111763236</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6219301175884318</v>
+        <v>0.01689739634298124</v>
       </c>
       <c r="N26" t="n">
-        <v>1.015255322884478</v>
+        <v>1.000217795778775</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6484069702669972</v>
+        <v>0.01761675348773446</v>
       </c>
       <c r="P26" t="n">
-        <v>231.8997101747953</v>
+        <v>170.3223829258698</v>
       </c>
       <c r="Q26" t="n">
-        <v>372.0704300346384</v>
+        <v>264.1758214407212</v>
       </c>
     </row>
   </sheetData>
